--- a/src/main/resources/output.xlsx
+++ b/src/main/resources/output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
   <si>
     <t>employee_id</t>
   </si>
@@ -119,7 +119,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>34.28</t>
+    <t/>
   </si>
   <si>
     <t>61000</t>
@@ -137,9 +137,6 @@
     <t>38</t>
   </si>
   <si>
-    <t>63166.67</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>39000</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
@@ -221,9 +215,6 @@
     <t>55000</t>
   </si>
   <si>
-    <t>9.26</t>
-  </si>
-  <si>
     <t>74</t>
   </si>
   <si>
@@ -282,12 +273,6 @@
   </si>
   <si>
     <t>86</t>
-  </si>
-  <si>
-    <t>10.5</t>
-  </si>
-  <si>
-    <t>78.55</t>
   </si>
 </sst>
 </file>
@@ -352,8 +337,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.0546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="4.29296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="7.7265625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.09375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.99609375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true" bestFit="true"/>
@@ -525,10 +510,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>41</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>42</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>27</v>
@@ -540,7 +525,7 @@
         <v>22</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +533,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>45</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>8</v>
@@ -563,50 +548,50 @@
         <v>13</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="D9" t="s" s="0">
         <v>49</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>51</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>22</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="C10" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s" s="0">
         <v>53</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>55</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>27</v>
@@ -618,7 +603,7 @@
         <v>28</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -626,10 +611,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>39</v>
@@ -644,18 +629,18 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>60</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>62</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>16</v>
@@ -670,21 +655,21 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>27</v>
@@ -696,21 +681,21 @@
         <v>22</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>20</v>
@@ -722,21 +707,21 @@
         <v>14</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s" s="0">
         <v>71</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>74</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>27</v>
@@ -748,18 +733,18 @@
         <v>28</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s" s="0">
         <v>74</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>77</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>34</v>
@@ -774,12 +759,12 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>17</v>
@@ -805,7 +790,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>9</v>
@@ -834,13 +819,13 @@
         <v>26</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>27</v>
@@ -852,18 +837,18 @@
         <v>28</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>8</v>
@@ -878,21 +863,21 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -904,33 +889,33 @@
         <v>22</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>91</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/output.xlsx
+++ b/src/main/resources/output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>employee_id</t>
   </si>
@@ -119,36 +119,42 @@
     <t>5</t>
   </si>
   <si>
+    <t>33.95</t>
+  </si>
+  <si>
+    <t>61000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>62210.53</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>39000</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>61000</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>39000</t>
-  </si>
-  <si>
     <t>60</t>
   </si>
   <si>
@@ -215,6 +221,9 @@
     <t>55000</t>
   </si>
   <si>
+    <t>8.95</t>
+  </si>
+  <si>
     <t>74</t>
   </si>
   <si>
@@ -273,6 +282,12 @@
   </si>
   <si>
     <t>86</t>
+  </si>
+  <si>
+    <t>10.05</t>
+  </si>
+  <si>
+    <t>78.24</t>
   </si>
 </sst>
 </file>
@@ -337,8 +352,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.9296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="4.29296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="7.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.0546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.3984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.09375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.99609375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="7.5546875" customWidth="true" bestFit="true"/>
@@ -510,10 +525,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>27</v>
@@ -525,7 +540,7 @@
         <v>22</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -533,10 +548,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>8</v>
@@ -548,50 +563,50 @@
         <v>13</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>22</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>27</v>
@@ -603,7 +618,7 @@
         <v>28</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -611,10 +626,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>39</v>
@@ -629,18 +644,18 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>16</v>
@@ -655,21 +670,21 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>27</v>
@@ -681,21 +696,21 @@
         <v>22</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>20</v>
@@ -707,21 +722,21 @@
         <v>14</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>27</v>
@@ -733,18 +748,18 @@
         <v>28</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>34</v>
@@ -759,12 +774,12 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>17</v>
@@ -790,7 +805,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>9</v>
@@ -819,13 +834,13 @@
         <v>26</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>27</v>
@@ -837,18 +852,18 @@
         <v>28</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>8</v>
@@ -863,21 +878,21 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -889,33 +904,33 @@
         <v>22</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
